--- a/Region3Spots.xlsx
+++ b/Region3Spots.xlsx
@@ -397,10 +397,627 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C56"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name of challenge</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Route Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Map?</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Challenge 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Route 101</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Challenge 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Route 103</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Challenge 3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Route 102</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Route 104</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Challenge 5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Petalburg Woods</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Challenge 6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Route 116</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Rustboro Gym</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Granite Cave</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Challenge 9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Tiny Fishing Spot</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Challenge 10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Dewford Gym</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Challenge 11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Route 107</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mauville Gym</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Challenge 13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Route 110</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Challenge 14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Route 117</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Challenge 15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Route 111</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Challenge 16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Lavaridge Gym</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Challenge 17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Fiery Path</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Challenge 18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Jagged Pass</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Challenge 19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Route 113</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Route 114</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Challenge 21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Meteor Falls</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Route 115</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Petalburg Gym</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Route 118</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Small Fishing Spot</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Route 119</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Route 120</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Route 121</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Safari Zone East</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Challenge 30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Mount Pyre</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Route 123</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Fortree Gym</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Mossdeep Gym</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Challenge 34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Big Fishing Spot</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Underwater Fishing Spot</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Sootopolis Gym</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Shoal Cave</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Challenge 41</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Mirage Island</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Sky Pillar</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Victory Road</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Hoenn Pokemon League</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Mauville Game Corner</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Starter Sanctuary</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Daycare Special Spot</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Battle Frontier Facility</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Weather Climax Cave</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Extra Challenge B 1</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Trick House</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Extra Challenge B 2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Rustboro Fossil Lab</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Extra Challenge B 3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Abandoned Ship</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Enemy Hideout</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Extra Challenge B 5</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Sealed Chamber</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Extra Challenge B 6</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Ancient Ruins</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Extra Challenge (Roaming)</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Roaming Hoenn Skies</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Nebula Fissure Challenge</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Nebula Fissure</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Region3Spots.xlsx
+++ b/Region3Spots.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -888,10 +888,10 @@
         <v>Extra Challenge A 3</v>
       </c>
       <c r="B45" t="str">
-        <v>Daycare Special Spot</v>
+        <v>Advanced Starter Sanctuary</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -899,7 +899,7 @@
         <v>Extra Challenge A 4</v>
       </c>
       <c r="B46" t="str">
-        <v>Battle Frontier Facility</v>
+        <v>Daycare Special Spot</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>Extra Challenge A 5</v>
       </c>
       <c r="B47" t="str">
-        <v>Weather Climax Cave</v>
+        <v>Battle Frontier Facility</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B48" t="str">
-        <v>Trick House</v>
+        <v>Weather Climax Cave</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B49" t="str">
-        <v>Rustboro Fossil Lab</v>
+        <v>Trick House</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extra Challenge B 3</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B50" t="str">
-        <v>Abandoned Ship</v>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extra Challenge B 4</v>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B51" t="str">
-        <v>Enemy Hideout</v>
+        <v>Abandoned Ship</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Extra Challenge B 5</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B52" t="str">
-        <v>Sealed Chamber</v>
+        <v>Enemy Hideout</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Extra Challenge B 6</v>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B53" t="str">
-        <v>Ancient Ruins</v>
+        <v>Sealed Chamber</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Extra Challenge (Roaming)</v>
+        <v>Extra Challenge B 6</v>
       </c>
       <c r="B54" t="str">
-        <v>Roaming Hoenn Skies</v>
+        <v>Ancient Ruins</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="B55" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Roaming Hoenn Skies</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1006,18 +1006,29 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>Nebula Fissure Challenge</v>
       </c>
-      <c r="B56" t="str">
+      <c r="B57" t="str">
         <v>Nebula Fissure</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C57"/>
   </ignoredErrors>
 </worksheet>
 </file>